--- a/api/2/clv2/xlsx/fr/FinanceType.xlsx
+++ b/api/2/clv2/xlsx/fr/FinanceType.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="201">
   <si>
     <t>code</t>
   </si>
@@ -245,6 +245,15 @@
   </si>
   <si>
     <t>Incluant les dettes convertibles et les actions.</t>
+  </si>
+  <si>
+    <t>434</t>
+  </si>
+  <si>
+    <t>Capital hybride multilatéral</t>
+  </si>
+  <si>
+    <t>Instruments de capital hybride émis par des institutions multilatérales</t>
   </si>
   <si>
     <t>451</t>
@@ -939,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1369,11 +1378,14 @@
       <c r="B28" t="s">
         <v>78</v>
       </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1384,7 +1396,7 @@
         <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="E29" t="s">
         <v>18</v>
@@ -1392,10 +1404,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s">
         <v>37</v>
@@ -1406,44 +1418,44 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" t="s">
         <v>86</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" t="s">
         <v>88</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E32" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" t="s">
         <v>90</v>
-      </c>
-      <c r="B33" t="s">
-        <v>91</v>
-      </c>
-      <c r="D33" t="s">
-        <v>87</v>
       </c>
       <c r="E33" t="s">
         <v>18</v>
@@ -1451,19 +1463,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" t="s">
         <v>94</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1477,7 +1486,7 @@
         <v>97</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -1490,8 +1499,11 @@
       <c r="B36" t="s">
         <v>99</v>
       </c>
+      <c r="C36" t="s">
+        <v>100</v>
+      </c>
       <c r="D36" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -1505,7 +1517,7 @@
         <v>102</v>
       </c>
       <c r="D37" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -1513,13 +1525,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D38" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -1527,13 +1539,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D39" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -1541,13 +1553,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D40" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -1555,13 +1567,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D41" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -1569,13 +1581,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D42" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -1583,13 +1595,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D43" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -1597,13 +1609,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B44" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D44" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -1611,13 +1623,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B45" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -1625,13 +1637,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -1639,13 +1651,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -1653,13 +1665,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D48" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -1667,13 +1679,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -1681,13 +1693,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B50" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D50" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -1695,13 +1707,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B51" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D51" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -1709,13 +1721,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B52" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -1723,13 +1735,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B53" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D53" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -1737,13 +1749,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B54" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D54" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -1751,13 +1763,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B55" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D55" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -1765,13 +1777,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B56" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D56" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -1779,13 +1791,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B57" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D57" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -1793,13 +1805,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B58" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D58" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -1807,13 +1819,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B59" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D59" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -1821,13 +1833,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B60" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D60" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -1835,13 +1847,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B61" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D61" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -1849,13 +1861,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B62" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D62" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -1863,16 +1875,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B63" t="s">
-        <v>154</v>
-      </c>
-      <c r="C63" t="s">
         <v>155</v>
       </c>
       <c r="D63" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -2004,11 +2013,14 @@
       <c r="B71" t="s">
         <v>178</v>
       </c>
+      <c r="C71" t="s">
+        <v>179</v>
+      </c>
       <c r="D71" t="s">
-        <v>179</v>
+        <v>15</v>
       </c>
       <c r="E71" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2019,7 +2031,7 @@
         <v>181</v>
       </c>
       <c r="D72" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E72" t="s">
         <v>18</v>
@@ -2027,13 +2039,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
+        <v>183</v>
+      </c>
+      <c r="B73" t="s">
+        <v>184</v>
+      </c>
+      <c r="D73" t="s">
         <v>182</v>
-      </c>
-      <c r="B73" t="s">
-        <v>183</v>
-      </c>
-      <c r="D73" t="s">
-        <v>179</v>
       </c>
       <c r="E73" t="s">
         <v>18</v>
@@ -2041,13 +2053,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B74" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D74" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E74" t="s">
         <v>18</v>
@@ -2061,7 +2073,7 @@
         <v>188</v>
       </c>
       <c r="D75" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E75" t="s">
         <v>18</v>
@@ -2069,13 +2081,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
+        <v>190</v>
+      </c>
+      <c r="B76" t="s">
+        <v>191</v>
+      </c>
+      <c r="D76" t="s">
         <v>189</v>
-      </c>
-      <c r="B76" t="s">
-        <v>190</v>
-      </c>
-      <c r="D76" t="s">
-        <v>191</v>
       </c>
       <c r="E76" t="s">
         <v>18</v>
@@ -2089,7 +2101,7 @@
         <v>193</v>
       </c>
       <c r="D77" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E77" t="s">
         <v>18</v>
@@ -2097,13 +2109,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
+        <v>195</v>
+      </c>
+      <c r="B78" t="s">
+        <v>196</v>
+      </c>
+      <c r="D78" t="s">
         <v>194</v>
-      </c>
-      <c r="B78" t="s">
-        <v>195</v>
-      </c>
-      <c r="D78" t="s">
-        <v>191</v>
       </c>
       <c r="E78" t="s">
         <v>18</v>
@@ -2111,15 +2123,29 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B79" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D79" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E79" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>199</v>
+      </c>
+      <c r="B80" t="s">
+        <v>200</v>
+      </c>
+      <c r="D80" t="s">
+        <v>194</v>
+      </c>
+      <c r="E80" t="s">
         <v>18</v>
       </c>
     </row>
